--- a/reports/devops-juniors-israel-2026-W28.xlsx
+++ b/reports/devops-juniors-israel-2026-W28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-06T10:58:29</t>
+    <t xml:space="preserve">2026-07-07T09:59:24</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -106,9 +106,6 @@
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -184,9 +181,39 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
@@ -220,739 +247,718 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpDesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Afternoon Shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-afternoon-shift-at-workiz-4437123104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-commit-4435577338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4435466755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4431969351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36097)</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, GCP, Cloud (any), Kubernetes, CI/CD, Terraform/IaC, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4437143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36781)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36792)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator - 240769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-240769-at-experis-israel-4433924358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Kubernetes, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HelpDesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (35684)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-35684-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436997608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-commit-4435577338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
     <t xml:space="preserve">Genie</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4425768937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firon Law Firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-firon-law-firm-4435571799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4429852518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-bynet-data-communications-4434515554</t>
   </si>
   <si>
     <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
@@ -967,28 +973,10 @@
     <t xml:space="preserve">2026-06-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Technologies | נס טכנולוגיות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-ness-technologies-%D7%A0%D7%A1-%D7%98%D7%9B%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%95%D7%AA-4433923361</t>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1000,54 +988,48 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -1057,21 +1039,24 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1091,9 +1076,6 @@
   </si>
   <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1233,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -1241,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1249,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1257,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10">
@@ -1347,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1375,36 +1357,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1417,7 +1391,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1429,34 +1403,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1464,13 +1438,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
@@ -1479,16 +1453,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1496,13 +1470,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
@@ -1511,16 +1485,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1528,31 +1502,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1560,31 +1534,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1592,31 +1566,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1604,7 @@
         <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1639,16 +1613,16 @@
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1656,31 +1630,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1688,31 +1662,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1720,31 +1694,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -1752,31 +1726,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -1784,19 +1758,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>99</v>
@@ -1808,7 +1782,7 @@
         <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1816,31 +1790,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>52</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -1848,31 +1822,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -1883,28 +1857,28 @@
         <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1912,31 +1886,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -1944,31 +1918,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
@@ -1976,31 +1950,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -2008,31 +1982,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -2040,31 +2014,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
@@ -2072,31 +2046,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -2104,31 +2078,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
@@ -2136,31 +2110,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
         <v>30</v>
       </c>
-      <c r="F23" s="3">
-        <v>41</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
@@ -2168,31 +2142,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
@@ -2200,31 +2174,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26">
@@ -2232,31 +2206,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2295,7 +2269,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2309,48 +2283,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -2359,33 +2333,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K2" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -2394,127 +2368,127 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K3" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K4" s="3">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K5" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2525,7 +2499,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2534,159 +2508,159 @@
         <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K10" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
         <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="K11" s="3">
         <v>7</v>
@@ -2694,25 +2668,25 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2721,80 +2695,80 @@
         <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>52</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K13" s="3">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -2802,1305 +2776,1305 @@
         <v>109</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K16" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="K17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K18" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="K20" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="K21" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="K22" s="3">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
         <v>30</v>
       </c>
-      <c r="E23" s="3">
-        <v>41</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="K24" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K26" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K27" s="3">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="K28" s="3">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="K30" s="3">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="K31" s="3">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>187</v>
+        <v>71</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="K32" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K33" s="3">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K35" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="K37" s="3">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="K38" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>223</v>
+        <v>59</v>
       </c>
       <c r="K39" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c r="K41" s="3">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="K42" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="K43" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>241</v>
+        <v>59</v>
       </c>
       <c r="K44" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="K45" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>147</v>
+        <v>252</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="K46" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>251</v>
+        <v>67</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K47" s="3">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>256</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>254</v>
       </c>
       <c r="K48" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>262</v>
+        <v>117</v>
       </c>
       <c r="K49" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>267</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>268</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>269</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4112,30 +4086,30 @@
         <v>274</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>275</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="K52" s="3">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4144,22 +4118,22 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>279</v>
+        <v>76</v>
       </c>
       <c r="K53" s="3">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -4170,7 +4144,7 @@
         <v>281</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4179,54 +4153,54 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="K54" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>58</v>
+        <v>286</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="K55" s="3">
         <v>5</v>
@@ -4234,34 +4208,34 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>198</v>
+        <v>290</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="K56" s="3">
         <v>28</v>
@@ -4269,153 +4243,153 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="K57" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>178</v>
+        <v>294</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="K58" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>296</v>
+        <v>67</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="K59" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K60" s="3">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4424,33 +4398,33 @@
         <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="K61" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4459,33 +4433,33 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="K62" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4494,131 +4468,59 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K63" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>317</v>
+        <v>125</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="K64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K66"/>
+  <autoFilter ref="A1:K64"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4683,8 +4585,6 @@
     <hyperlink ref="I62" r:id="rId61"/>
     <hyperlink ref="I63" r:id="rId62"/>
     <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4692,9 +4592,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4703,282 +4603,213 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>37</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3">
-        <v>52</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>298</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>221</v>
+        <v>296</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>225</v>
+        <v>299</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4988,9 +4819,6 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5005,164 +4833,164 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>344</v>
@@ -5170,13 +4998,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5193,13 +5021,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
@@ -5210,7 +5038,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
@@ -5218,10 +5046,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
@@ -5232,7 +5060,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -5243,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6">
@@ -5254,18 +5082,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -5283,51 +5100,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W28.xlsx
+++ b/reports/devops-juniors-israel-2026-W28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="346">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-07T09:59:24</t>
+    <t xml:space="preserve">2026-07-08T08:43:40</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -145,6 +148,42 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -163,24 +202,6 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -214,12 +235,45 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -247,15 +301,27 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
     <t xml:space="preserve">Google</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
   </si>
   <si>
@@ -265,6 +331,18 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-gotfriends-4434530772</t>
+  </si>
+  <si>
     <t xml:space="preserve">Computer System Engineer</t>
   </si>
   <si>
@@ -283,30 +361,60 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36781)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36792)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transmitsecurity</t>
   </si>
   <si>
@@ -343,18 +451,6 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
   </si>
   <si>
@@ -370,525 +466,414 @@
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-logica-it-4432768849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracom Telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida, Florida, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HelpDesk</t>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Afternoon Shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-afternoon-shift-at-workiz-4437123104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-commit-4435577338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -910,112 +895,100 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4435466755</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4431969351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-bynet-data-communications-4434515554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1024,15 +997,6 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -1051,10 +1015,10 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1088,9 +1052,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1176,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10">
@@ -1321,7 +1282,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -1337,7 +1298,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1371,7 +1332,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -1379,7 +1340,15 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>5</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1360,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1403,34 +1372,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1438,31 +1407,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1470,31 +1439,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1502,31 +1471,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1534,13 +1503,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1549,16 +1518,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1566,31 +1535,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1598,31 +1567,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1630,31 +1599,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1662,19 +1631,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>86</v>
@@ -1697,28 +1666,28 @@
         <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1726,31 +1695,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -1758,31 +1727,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1790,31 +1759,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1822,31 +1791,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1854,31 +1823,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1886,31 +1855,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1918,31 +1887,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1950,31 +1919,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1982,31 +1951,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -2014,19 +1983,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>135</v>
@@ -2035,10 +2004,10 @@
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -2046,31 +2015,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
@@ -2078,31 +2047,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23">
@@ -2110,31 +2079,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
@@ -2142,31 +2111,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -2174,31 +2143,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
@@ -2206,31 +2175,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2269,7 +2238,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2283,153 +2252,153 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2438,150 +2407,150 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2593,7 +2562,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2601,710 +2570,710 @@
         <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K11" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>135</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K20" s="3">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="K23" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K24" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="K25" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="K26" s="3">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K27" s="3">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="K28" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3313,103 +3282,103 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K30" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
         <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K31" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="K32" s="3">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3418,68 +3387,68 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="K33" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>96</v>
+        <v>207</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="K34" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3488,33 +3457,33 @@
         <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K35" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3523,33 +3492,33 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K36" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>27</v>
@@ -3558,36 +3527,36 @@
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K37" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
@@ -3596,170 +3565,170 @@
         <v>219</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="K38" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="K39" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="K40" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="K41" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>238</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3768,33 +3737,33 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>243</v>
+        <v>66</v>
       </c>
       <c r="K43" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3803,33 +3772,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K44" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3838,68 +3807,68 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="K46" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3908,33 +3877,33 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K47" s="3">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3943,33 +3912,33 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="K48" s="3">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>241</v>
+        <v>52</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -3978,33 +3947,33 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="K49" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>266</v>
+        <v>106</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4013,33 +3982,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="K50" s="3">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4048,264 +4017,264 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="K51" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K52" s="3">
         <v>6</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="K52" s="3">
-        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="K53" s="3">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="K54" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="K55" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>172</v>
+        <v>295</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>291</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>293</v>
+        <v>114</v>
       </c>
       <c r="K56" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>294</v>
+        <v>185</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4313,214 +4282,39 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>67</v>
+        <v>225</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>302</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="K60" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="K63" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="3">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K64" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K64"/>
+  <autoFilter ref="A1:K59"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4580,11 +4374,6 @@
     <hyperlink ref="I57" r:id="rId56"/>
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4592,9 +4381,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4603,194 +4392,194 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -4799,13 +4588,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4833,178 +4622,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>296</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>239</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5021,13 +4810,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2">
@@ -5035,10 +4824,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
@@ -5049,7 +4838,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4">
@@ -5057,10 +4846,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
@@ -5071,7 +4860,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6">
@@ -5082,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -5100,16 +4889,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
@@ -5117,10 +4906,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5129,22 +4918,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>358</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W28.xlsx
+++ b/reports/devops-juniors-israel-2026-W28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="384">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-08T08:43:40</t>
+    <t xml:space="preserve">2026-07-09T10:06:24</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -148,6 +148,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
@@ -166,835 +184,937 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
     <t xml:space="preserve">Confidential Careers</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-gotfriends-4434530772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36781)</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpDesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (36802)</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36792)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+    <t xml:space="preserve">Linux, Azure, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-36802-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438216870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer (Student)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4686004006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Afternoon Shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-afternoon-shift-at-workiz-4437123104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyndryl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-kyndryl-4437305734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safer Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracom Telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida, Florida, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4435625940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-logica-it-4432768849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracom Telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida, Florida, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438218736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Site Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
     <t xml:space="preserve">Genie</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4435466755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תומך/ת Help Desk וטכנאי/ת PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%95%D7%9E%D7%9A-%D7%AA-help-desk%C2%A0%D7%95%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-pc-at-accel-solutions-4431094783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
@@ -1003,22 +1123,16 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1176,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1184,7 +1298,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1192,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1200,7 +1314,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10">
@@ -1282,7 +1396,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -1290,7 +1404,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1298,7 +1412,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1332,7 +1446,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
@@ -1340,7 +1454,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1360,7 +1474,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1416,7 +1530,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1448,7 +1562,7 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1477,25 +1591,25 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1503,13 +1617,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1544,10 +1658,10 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
@@ -1579,7 +1693,7 @@
         <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>76</v>
@@ -1608,10 +1722,10 @@
         <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>82</v>
@@ -1631,19 +1745,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>86</v>
@@ -1672,10 +1786,10 @@
         <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>92</v>
@@ -1701,25 +1815,25 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>68</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>74</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -1733,7 +1847,7 @@
         <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>28</v>
@@ -1759,31 +1873,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1791,31 +1905,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1823,31 +1937,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -1855,31 +1969,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17">
@@ -1890,28 +2004,28 @@
         <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1919,31 +2033,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1951,31 +2065,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1983,31 +2097,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
@@ -2015,31 +2129,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -2047,31 +2161,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -2079,31 +2193,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -2111,13 +2225,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
@@ -2126,16 +2240,16 @@
         <v>32</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
@@ -2143,13 +2257,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2158,16 +2272,16 @@
         <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
@@ -2175,31 +2289,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2239,7 +2353,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2252,7 +2366,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2267,22 +2381,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2296,7 +2410,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2305,7 +2419,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2317,7 +2431,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -2331,7 +2445,7 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2340,7 +2454,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2352,7 +2466,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -2363,42 +2477,42 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K4" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2410,7 +2524,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2422,7 +2536,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -2436,16 +2550,16 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2457,7 +2571,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -2474,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2492,7 +2606,7 @@
         <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2506,16 +2620,16 @@
         <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2527,30 +2641,30 @@
         <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2562,7 +2676,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2576,16 +2690,16 @@
         <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2597,7 +2711,7 @@
         <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2608,31 +2722,31 @@
         <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>68</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3">
-        <v>74</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -2643,7 +2757,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>28</v>
@@ -2655,7 +2769,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2667,109 +2781,109 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K14" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
         <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
@@ -2777,37 +2891,37 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="K16" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -2815,255 +2929,255 @@
         <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="K19" s="3">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="K20" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K21" s="3">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="K22" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
@@ -3072,33 +3186,33 @@
         <v>32</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="K24" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -3107,68 +3221,68 @@
         <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K25" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="K26" s="3">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
@@ -3177,159 +3291,159 @@
         <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>75</v>
+        <v>184</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K28" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="K31" s="3">
         <v>21</v>
@@ -3337,10 +3451,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>75</v>
@@ -3349,407 +3463,407 @@
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K32" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K33" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K34" s="3">
         <v>55</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>73</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="K35" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K36" s="3">
         <v>55</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="K37" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>49</v>
+        <v>228</v>
       </c>
       <c r="K38" s="3">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="K39" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="K40" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="K41" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>242</v>
+        <v>143</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>10</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="G43" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K43" s="3">
         <v>45</v>
@@ -3757,25 +3871,25 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
@@ -3784,33 +3898,33 @@
         <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="K44" s="3">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>249</v>
+        <v>139</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
@@ -3819,138 +3933,138 @@
         <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>6</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="K46" s="3">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>262</v>
+        <v>60</v>
       </c>
       <c r="K47" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="G48" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="K48" s="3">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
@@ -3959,362 +4073,679 @@
         <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="K49" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>149</v>
+        <v>275</v>
       </c>
       <c r="K50" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>274</v>
+        <v>95</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>279</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="G52" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="K52" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>10</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="3">
-        <v>4</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>288</v>
+        <v>88</v>
       </c>
       <c r="K53" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="J54" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="3">
-        <v>4</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="3">
+        <v>8</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="K55" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>295</v>
+        <v>75</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>114</v>
+        <v>290</v>
       </c>
       <c r="K56" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>185</v>
+        <v>298</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="K57" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="J59" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K59" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="K60" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K61" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K64" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K65" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K66" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K67" s="3">
         <v>44</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K68" s="3">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K59"/>
+  <autoFilter ref="A1:K68"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4374,6 +4805,15 @@
     <hyperlink ref="I57" r:id="rId56"/>
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4381,9 +4821,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4404,10 +4844,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4415,190 +4855,282 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>304</v>
+        <v>139</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4608,6 +5140,10 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4622,178 +5158,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>321</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>239</v>
+        <v>361</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>324</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4813,10 +5349,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -4824,10 +5360,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3">
@@ -4835,10 +5371,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4">
@@ -4846,10 +5382,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5">
@@ -4860,7 +5396,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6">
@@ -4871,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4892,13 +5428,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -4906,10 +5442,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4918,10 +5454,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4933,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W28.xlsx
+++ b/reports/devops-juniors-israel-2026-W28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-09T10:06:24</t>
+    <t xml:space="preserve">2026-07-10T09:52:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -184,6 +184,24 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -199,940 +217,916 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-coralogix-4431747155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Kubernetes, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-dream-4427425550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438599279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (36802)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-36802-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438216870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer (Student)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4686004006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-gong-4438277123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyndryl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-kyndryl-4437305734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safer Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4434851492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-vast-data-4343803811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracom Telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida, Florida, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4435625940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438218736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Site Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HelpDesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (36802)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-36802-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438216870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer (Student)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4686004006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Afternoon Shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-afternoon-shift-at-workiz-4437123104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyndryl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-kyndryl-4437305734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safer Place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracom Telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida, Florida, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 2 Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technician-at-solaredge-technologies-4431252112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4431962533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-3785660099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4435625940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438218736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multimedia Systems &amp; IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/multimedia-systems-it-support-specialist-at-deloitte-4433302126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1290,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1298,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1306,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -1314,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10">
@@ -1396,7 +1390,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1404,7 +1398,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1412,7 +1406,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1446,7 +1440,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
@@ -1591,7 +1585,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1600,16 +1594,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1617,13 +1611,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1661,7 +1655,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
@@ -1681,31 +1675,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>80</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1713,31 +1707,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1745,13 +1739,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1777,31 +1771,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>76</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3">
-        <v>74</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1809,31 +1803,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -1841,31 +1835,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="3">
-        <v>57</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1873,31 +1867,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="3">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1905,31 +1899,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1937,31 +1931,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -1972,10 +1966,10 @@
         <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -1984,16 +1978,16 @@
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -2001,31 +1995,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
@@ -2033,31 +2027,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
@@ -2065,31 +2059,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
         <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -2097,13 +2091,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -2112,16 +2106,16 @@
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2129,31 +2123,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
@@ -2161,31 +2155,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -2193,31 +2187,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24">
@@ -2225,13 +2219,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
@@ -2240,16 +2234,16 @@
         <v>32</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
@@ -2257,13 +2251,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2272,16 +2266,16 @@
         <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
@@ -2289,13 +2283,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2304,16 +2298,16 @@
         <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2352,8 +2346,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2366,7 +2360,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2381,22 +2375,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
@@ -2419,7 +2413,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2431,7 +2425,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -2454,7 +2448,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2466,7 +2460,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -2477,7 +2471,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2486,33 +2480,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2524,7 +2518,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2536,7 +2530,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -2553,13 +2547,13 @@
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2571,88 +2565,88 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>80</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K8" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2664,7 +2658,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2676,39 +2670,39 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>76</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>74</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="K10" s="3">
         <v>1</v>
@@ -2716,177 +2710,177 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K11" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>68</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="3">
-        <v>57</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3">
+        <v>57</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="K13" s="3">
         <v>56</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K13" s="3">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K15" s="3">
-        <v>9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -2894,10 +2888,10 @@
         <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
@@ -2906,138 +2900,138 @@
         <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K16" s="3">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K17" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="K18" s="3">
-        <v>25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
         <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="K19" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -3046,138 +3040,138 @@
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="K20" s="3">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K21" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K22" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="K23" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
@@ -3186,33 +3180,33 @@
         <v>32</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -3221,33 +3215,33 @@
         <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3256,68 +3250,68 @@
         <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K27" s="3">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -3326,33 +3320,33 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="K28" s="3">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
@@ -3361,68 +3355,68 @@
         <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3431,33 +3425,33 @@
         <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K31" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3466,33 +3460,33 @@
         <v>27</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3501,33 +3495,33 @@
         <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3536,138 +3530,138 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="K34" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="K35" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>219</v>
+        <v>69</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K36" s="3">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
@@ -3676,54 +3670,54 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -3731,13 +3725,13 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>75</v>
+        <v>203</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3746,33 +3740,33 @@
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3781,19 +3775,19 @@
         <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K41" s="3">
         <v>1</v>
@@ -3801,328 +3795,328 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="K43" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>67</v>
+        <v>238</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="K44" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3">
         <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E46" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>94</v>
+        <v>251</v>
       </c>
       <c r="K46" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>13</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>10</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="K47" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="K48" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>266</v>
+        <v>67</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>140</v>
+        <v>264</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>95</v>
+        <v>267</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>63</v>
+        <v>269</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4131,33 +4125,33 @@
         <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K51" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4166,33 +4160,33 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="K52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4201,33 +4195,33 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>288</v>
+        <v>97</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4236,173 +4230,173 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="K54" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>291</v>
+        <v>159</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>283</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>292</v>
+        <v>85</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>261</v>
+        <v>95</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>290</v>
+        <v>66</v>
       </c>
       <c r="K56" s="3">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>303</v>
+        <v>97</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K58" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>154</v>
+        <v>299</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4411,33 +4405,33 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>308</v>
+        <v>66</v>
       </c>
       <c r="K59" s="3">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4446,33 +4440,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>312</v>
+        <v>122</v>
       </c>
       <c r="K60" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>67</v>
+        <v>276</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4481,33 +4475,33 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="K61" s="3">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>317</v>
+        <v>227</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4516,33 +4510,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>94</v>
+        <v>310</v>
       </c>
       <c r="K62" s="3">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>321</v>
+        <v>184</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4551,33 +4545,33 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4586,138 +4580,138 @@
         <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K64" s="3">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>328</v>
+        <v>67</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>330</v>
+        <v>203</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="K65" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="K66" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>69</v>
+        <v>326</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="K67" s="3">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4726,26 +4720,131 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K68" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K69" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K68" s="3">
+      <c r="B70" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
         <v>3</v>
       </c>
+      <c r="F70" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K68"/>
+  <autoFilter ref="A1:K71"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4814,6 +4913,9 @@
     <hyperlink ref="I66" r:id="rId65"/>
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4821,8 +4923,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4844,10 +4946,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4855,79 +4957,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
@@ -4936,21 +5038,21 @@
         <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
@@ -4959,21 +5061,21 @@
         <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -4982,21 +5084,21 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -5005,132 +5107,86 @@
         <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>291</v>
+        <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5142,8 +5198,6 @@
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
     <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5158,178 +5212,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B4" s="3">
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>361</v>
+        <v>245</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>254</v>
+        <v>359</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5349,10 +5403,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -5360,10 +5414,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -5371,10 +5425,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -5382,10 +5436,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5">
@@ -5396,7 +5450,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6">
@@ -5407,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -5428,13 +5482,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -5445,7 +5499,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5454,10 +5508,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5469,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W28.xlsx
+++ b/reports/devops-juniors-israel-2026-W28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10T09:52:30</t>
+    <t xml:space="preserve">2026-07-12T08:31:02</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -115,1051 +115,976 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack you'll work with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, GCP, Cloud (any), Kubernetes, CI/CD, Terraform/IaC, Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438227753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer (Data Center)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-data-center-at-nebius-4429629836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpDesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyndryl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-kyndryl-4437305734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת IT Support (Help Desk) #996420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-it-support-help-desk-%23996420-at-gold-office-4436692061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safer Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-systems-engineer-at-ben-gurion-university-of-the-negev-4428645689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-Time IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeteorOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/part-time-it-support-engineer-at-meteorops-4435963853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (Contractor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards Lifesciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438218736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Site Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack you'll work with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-coralogix-4431747155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker, Kubernetes, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-dream-4427425550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438599279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (36802)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-36802-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438216870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer (Student)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4686004006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-gong-4438277123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyndryl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-kyndryl-4437305734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safer Place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4434851492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-vast-data-4343803811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wireless Systems Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracom Telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida, Florida, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-wireless-systems-technical-support-engineer-intracom-telecom-1134530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4435625940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4432333769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438218736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technician-at-solaredge-technologies-4431252112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4431962533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-3785660099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1292,7 +1217,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1300,7 +1225,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -1308,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10">
@@ -1390,7 +1315,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1398,7 +1323,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -1406,7 +1331,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1440,7 +1365,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
@@ -1448,15 +1373,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1385,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1480,34 +1397,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1515,13 +1432,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
@@ -1530,16 +1447,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1547,13 +1464,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
@@ -1562,16 +1479,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1579,31 +1496,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1611,31 +1528,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1643,31 +1560,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3">
-        <v>91</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1675,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>73</v>
@@ -1684,7 +1601,7 @@
         <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
         <v>88</v>
@@ -1713,13 +1630,13 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
@@ -1748,7 +1665,7 @@
         <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
         <v>76</v>
@@ -1771,16 +1688,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
         <v>76</v>
@@ -1812,22 +1729,22 @@
         <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
         <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -1835,7 +1752,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>96</v>
@@ -1847,7 +1764,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>98</v>
@@ -1859,7 +1776,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1867,19 +1784,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>103</v>
@@ -1891,7 +1808,7 @@
         <v>104</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1899,31 +1816,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>51</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1931,7 +1848,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>111</v>
@@ -1943,19 +1860,19 @@
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1963,31 +1880,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1995,31 +1912,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -2027,31 +1944,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
@@ -2059,31 +1976,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
@@ -2091,13 +2008,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -2106,16 +2023,16 @@
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -2123,31 +2040,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22">
@@ -2155,31 +2072,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23">
@@ -2187,31 +2104,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
@@ -2219,31 +2136,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
@@ -2251,31 +2168,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -2283,31 +2200,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
         <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2346,8 +2263,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2360,48 +2277,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -2410,33 +2327,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K2" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -2445,132 +2362,132 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K3" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>91</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>73</v>
@@ -2579,7 +2496,7 @@
         <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
         <v>88</v>
@@ -2588,7 +2505,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2600,7 +2517,7 @@
         <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -2611,19 +2528,19 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2635,7 +2552,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2649,7 +2566,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
         <v>76</v>
@@ -2658,7 +2575,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2670,21 +2587,21 @@
         <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
         <v>76</v>
@@ -2693,7 +2610,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2705,7 +2622,7 @@
         <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2719,33 +2636,33 @@
         <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
         <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>96</v>
@@ -2757,13 +2674,13 @@
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2772,33 +2689,33 @@
         <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="K12" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
@@ -2807,50 +2724,50 @@
         <v>104</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="K13" s="3">
-        <v>56</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>51</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K14" s="3">
-        <v>9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>111</v>
@@ -2862,176 +2779,176 @@
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K15" s="3">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K18" s="3">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K19" s="3">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -3040,1384 +2957,1384 @@
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="K20" s="3">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K21" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K24" s="3">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="K25" s="3">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
         <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="K26" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="K28" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="K29" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
         <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K32" s="3">
         <v>58</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>27</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="K35" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="K36" s="3">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="K37" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>91</v>
       </c>
       <c r="K38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>72</v>
+        <v>215</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>222</v>
+        <v>66</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>231</v>
+        <v>145</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>240</v>
+        <v>169</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>243</v>
+        <v>145</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K45" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="K46" s="3">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="K47" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>203</v>
+        <v>68</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>91</v>
+        <v>265</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>67</v>
+        <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>154</v>
+        <v>267</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>155</v>
+        <v>268</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E49" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="K49" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>123</v>
+        <v>272</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>264</v>
+        <v>74</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="K50" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E51" s="3">
         <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="K51" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>91</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>147</v>
+        <v>286</v>
       </c>
       <c r="K53" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>282</v>
+        <v>91</v>
       </c>
       <c r="K54" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="K55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>97</v>
+        <v>296</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E56" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="K56" s="3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E57" s="3">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K57" s="3">
         <v>10</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K57" s="3">
-        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K58" s="3">
         <v>10</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>299</v>
+        <v>74</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>66</v>
+        <v>313</v>
       </c>
       <c r="K59" s="3">
         <v>47</v>
@@ -4425,426 +4342,41 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="K60" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K61" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K62" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>6</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="3">
-        <v>6</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K64" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>6</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K65" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E67" s="3">
         <v>4</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K67" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="3">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K68" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K69" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K71" s="3">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K71"/>
+  <autoFilter ref="A1:K60"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4905,17 +4437,6 @@
     <hyperlink ref="I58" r:id="rId57"/>
     <hyperlink ref="I59" r:id="rId58"/>
     <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4923,8 +4444,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4934,259 +4455,190 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5195,9 +4647,6 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5212,178 +4661,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>347</v>
+        <v>302</v>
       </c>
       <c r="B4" s="3">
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>239</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>250</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B16" s="3">
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -5400,13 +4849,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
@@ -5414,10 +4863,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3">
@@ -5425,10 +4874,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -5436,10 +4885,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5">
@@ -5450,7 +4899,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
@@ -5461,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5479,16 +4928,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -5496,10 +4945,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5508,22 +4957,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D4" s="3"/>
     </row>
